--- a/MealPlanner/sprints/sprint3/Sprint Backlog & Burnup Chart.xlsx
+++ b/MealPlanner/sprints/sprint3/Sprint Backlog & Burnup Chart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://westga365-my.sharepoint.com/personal/jcorley_westga_edu/Documents/Teaching/Software Engineering II/SE2 - Spring 2026/Project/SE2-project-repos-sample/sprints/sprint1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jbatty1\Documents\GitHub\MealPlanner-CS3212-Group4\MealPlanner\sprints\sprint3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{9C9C4265-351C-41A0-89E5-93A08D9C51A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C68B4513-1541-415B-8F23-00764467EF2F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{518D727A-A746-4D31-802B-7217B6E8D807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>Related User Story</t>
   </si>
@@ -53,22 +51,25 @@
     <t>Week 2</t>
   </si>
   <si>
-    <t>Week 3</t>
-  </si>
-  <si>
-    <t>Week 4</t>
-  </si>
-  <si>
     <t>Amount Remaining After…</t>
   </si>
   <si>
     <t>Estimate Totals</t>
   </si>
   <si>
-    <t>Code Things…</t>
+    <t>View Meal</t>
   </si>
   <si>
-    <t>That User Story</t>
+    <t>Make meal serialization (Jareth)</t>
+  </si>
+  <si>
+    <t>Maintaince</t>
+  </si>
+  <si>
+    <t>Fix Tests (Jareth)</t>
+  </si>
+  <si>
+    <t>Fix Persistence on Logout (Jareth)</t>
   </si>
 </sst>
 </file>
@@ -266,21 +267,15 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$27:$G$27</c:f>
+              <c:f>Sheet1!$D$27:$E$27</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>25</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>100</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -309,21 +304,15 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$D$28:$G$28</c:f>
+              <c:f>Sheet1!$D$28:$E$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>100</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -463,7 +452,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -471,6 +459,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1065,13 +1054,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>100012</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>176212</xdr:rowOff>
@@ -1365,15 +1354,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="51.42578125" customWidth="1"/>
-    <col min="2" max="2" width="41.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="51.44140625" customWidth="1"/>
+    <col min="2" max="2" width="41.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1384,13 +1373,11 @@
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -1400,289 +1387,235 @@
       <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1">
         <v>5</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="D3" s="2">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1">
-        <v>100</v>
-      </c>
-      <c r="D3" s="2">
-        <v>25</v>
-      </c>
-      <c r="E3" s="2">
-        <v>50</v>
-      </c>
-      <c r="F3" s="2">
-        <v>75</v>
-      </c>
-      <c r="G3" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C27" s="3">
         <f>SUM(C3:C26)</f>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="D27" s="3">
-        <f t="shared" ref="D27:G27" si="0">SUM(D3:D26)</f>
-        <v>25</v>
+        <f t="shared" ref="D27:E27" si="0">SUM(D3:D26)</f>
+        <v>5</v>
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="F27" s="3">
-        <f t="shared" si="0"/>
-        <v>75</v>
-      </c>
-      <c r="G27" s="3">
-        <f t="shared" si="0"/>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D28">
         <f>$C$27</f>
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="E28">
-        <f t="shared" ref="E28:G28" si="1">$C$27</f>
-        <v>100</v>
-      </c>
-      <c r="F28">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="G28">
-        <f t="shared" si="1"/>
-        <v>100</v>
+        <f t="shared" ref="E28" si="1">$C$27</f>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="D1:E1"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A1:A2"/>
